--- a/Planificacion/BOM/BOM_C_R.xlsx
+++ b/Planificacion/BOM/BOM_C_R.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/92074c9dfb58844c/Documentos/UNIVERSIDAD/MASTER/1/TPI/SE/TP1-G1/Planificacion/BOM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="82" documentId="11_AD4DB114E441178AC67DF4E4CE12E26A693EDF2F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3C46B4CA-07F8-48D9-823B-2B0554B504DF}"/>
+  <xr:revisionPtr revIDLastSave="117" documentId="11_AD4DB114E441178AC67DF4E4CE12E26A693EDF2F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3740415D-D6F3-459F-8BA9-1FD9A9FA4A79}"/>
   <bookViews>
-    <workbookView xWindow="10140" yWindow="0" windowWidth="10455" windowHeight="11625" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="10455" windowHeight="11625" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="29">
   <si>
     <t xml:space="preserve">BOM </t>
   </si>
@@ -85,6 +85,33 @@
   </si>
   <si>
     <t>3646454RL</t>
+  </si>
+  <si>
+    <t>10uF</t>
+  </si>
+  <si>
+    <t>33k</t>
+  </si>
+  <si>
+    <t>100R</t>
+  </si>
+  <si>
+    <t>12K</t>
+  </si>
+  <si>
+    <t>1K5</t>
+  </si>
+  <si>
+    <t>180R</t>
+  </si>
+  <si>
+    <t>330R</t>
+  </si>
+  <si>
+    <t>130R</t>
+  </si>
+  <si>
+    <t>68R</t>
   </si>
 </sst>
 </file>
@@ -491,10 +518,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B1:O16"/>
+  <dimension ref="B1:O20"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="5" max="5" width="31.85546875" customWidth="1"/>
+    <col min="5" max="5" width="19.85546875" customWidth="1"/>
     <col min="6" max="6" width="33.85546875" customWidth="1"/>
     <col min="7" max="7" width="27.28515625" customWidth="1"/>
     <col min="13" max="13" width="17.5703125" customWidth="1"/>
@@ -653,6 +680,15 @@
       <c r="D9">
         <v>805</v>
       </c>
+      <c r="E9" t="s">
+        <v>20</v>
+      </c>
+      <c r="F9">
+        <v>4166969</v>
+      </c>
+      <c r="G9" s="4">
+        <v>5.45E-2</v>
+      </c>
       <c r="L9">
         <v>805</v>
       </c>
@@ -712,20 +748,112 @@
       <c r="L13">
         <v>805</v>
       </c>
+      <c r="M13" t="s">
+        <v>21</v>
+      </c>
+      <c r="N13">
+        <v>3646498</v>
+      </c>
+      <c r="O13" s="4">
+        <v>5.6399999999999999E-2</v>
+      </c>
     </row>
     <row r="14" spans="2:15">
       <c r="L14">
         <v>805</v>
       </c>
+      <c r="M14" t="s">
+        <v>22</v>
+      </c>
+      <c r="N14">
+        <v>4148651</v>
+      </c>
+      <c r="O14" s="4">
+        <v>5.21E-2</v>
+      </c>
     </row>
     <row r="15" spans="2:15">
       <c r="L15">
         <v>805</v>
       </c>
+      <c r="M15" t="s">
+        <v>23</v>
+      </c>
+      <c r="N15">
+        <v>3603747</v>
+      </c>
+      <c r="O15" s="4">
+        <v>0.42</v>
+      </c>
     </row>
     <row r="16" spans="2:15">
       <c r="L16">
         <v>805</v>
+      </c>
+      <c r="M16" t="s">
+        <v>24</v>
+      </c>
+      <c r="N16">
+        <v>3603768</v>
+      </c>
+      <c r="O16" s="4">
+        <v>0.42</v>
+      </c>
+    </row>
+    <row r="17" spans="12:15">
+      <c r="L17">
+        <v>805</v>
+      </c>
+      <c r="M17" t="s">
+        <v>25</v>
+      </c>
+      <c r="N17">
+        <v>2380329</v>
+      </c>
+      <c r="O17" s="4">
+        <v>7.5300000000000006E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="12:15">
+      <c r="L18">
+        <v>805</v>
+      </c>
+      <c r="M18" t="s">
+        <v>26</v>
+      </c>
+      <c r="N18">
+        <v>1739223</v>
+      </c>
+      <c r="O18" s="4">
+        <v>0.27</v>
+      </c>
+    </row>
+    <row r="19" spans="12:15">
+      <c r="L19">
+        <v>805</v>
+      </c>
+      <c r="M19" t="s">
+        <v>27</v>
+      </c>
+      <c r="N19">
+        <v>1692530</v>
+      </c>
+      <c r="O19" s="4">
+        <v>3.4500000000000003E-2</v>
+      </c>
+    </row>
+    <row r="20" spans="12:15">
+      <c r="L20">
+        <v>805</v>
+      </c>
+      <c r="M20" t="s">
+        <v>28</v>
+      </c>
+      <c r="N20">
+        <v>4010184</v>
+      </c>
+      <c r="O20" s="4">
+        <v>4.7800000000000002E-2</v>
       </c>
     </row>
   </sheetData>

--- a/Planificacion/BOM/BOM_C_R.xlsx
+++ b/Planificacion/BOM/BOM_C_R.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/92074c9dfb58844c/Documentos/UNIVERSIDAD/MASTER/1/TPI/SE/TP1-G1/Planificacion/BOM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="117" documentId="11_AD4DB114E441178AC67DF4E4CE12E26A693EDF2F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3740415D-D6F3-459F-8BA9-1FD9A9FA4A79}"/>
+  <xr:revisionPtr revIDLastSave="121" documentId="11_AD4DB114E441178AC67DF4E4CE12E26A693EDF2F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{54A3ED60-D741-47C0-AB38-0B056B8F0FAB}"/>
   <bookViews>
     <workbookView xWindow="-105" yWindow="0" windowWidth="10455" windowHeight="11625" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="30">
   <si>
     <t xml:space="preserve">BOM </t>
   </si>
@@ -112,6 +112,9 @@
   </si>
   <si>
     <t>68R</t>
+  </si>
+  <si>
+    <t>1uF</t>
   </si>
 </sst>
 </file>
@@ -703,6 +706,18 @@
       </c>
     </row>
     <row r="10" spans="2:15">
+      <c r="D10">
+        <v>805</v>
+      </c>
+      <c r="E10" t="s">
+        <v>29</v>
+      </c>
+      <c r="F10">
+        <v>2773213</v>
+      </c>
+      <c r="G10" s="4">
+        <v>7.3599999999999999E-2</v>
+      </c>
       <c r="L10">
         <v>805</v>
       </c>

--- a/Planificacion/BOM/BOM_C_R.xlsx
+++ b/Planificacion/BOM/BOM_C_R.xlsx
@@ -1,21 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/92074c9dfb58844c/Documentos/UNIVERSIDAD/MASTER/1/TPI/SE/TP1-G1/Planificacion/BOM/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Invitado(pass user)\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="121" documentId="11_AD4DB114E441178AC67DF4E4CE12E26A693EDF2F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{54A3ED60-D741-47C0-AB38-0B056B8F0FAB}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="10455" windowHeight="11625" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12435"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="152511"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -25,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="34">
   <si>
     <t xml:space="preserve">BOM </t>
   </si>
@@ -115,16 +114,28 @@
   </si>
   <si>
     <t>1uF</t>
+  </si>
+  <si>
+    <t>6k8</t>
+  </si>
+  <si>
+    <t>1k2</t>
+  </si>
+  <si>
+    <t>820R</t>
+  </si>
+  <si>
+    <t>150R</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0.000\ &quot;€&quot;;[Red]\-#,##0.000\ &quot;€&quot;"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -142,6 +153,12 @@
       <sz val="10"/>
       <color rgb="FF161616"/>
       <name val="Inherit"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF161616"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="4">
@@ -224,7 +241,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
@@ -237,6 +254,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -520,8 +538,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B1:O20"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="B1:O24"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col min="5" max="5" width="19.85546875" customWidth="1"/>
@@ -871,8 +889,64 @@
         <v>4.7800000000000002E-2</v>
       </c>
     </row>
+    <row r="21" spans="12:15">
+      <c r="L21">
+        <v>805</v>
+      </c>
+      <c r="M21" t="s">
+        <v>30</v>
+      </c>
+      <c r="N21" s="8">
+        <v>3603685</v>
+      </c>
+      <c r="O21" s="8">
+        <v>0.36599999999999999</v>
+      </c>
+    </row>
+    <row r="22" spans="12:15">
+      <c r="L22">
+        <v>805</v>
+      </c>
+      <c r="M22" t="s">
+        <v>31</v>
+      </c>
+      <c r="N22" s="8">
+        <v>3603492</v>
+      </c>
+      <c r="O22" s="8">
+        <v>0.36599999999999999</v>
+      </c>
+    </row>
+    <row r="23" spans="12:15">
+      <c r="L23">
+        <v>805</v>
+      </c>
+      <c r="M23" t="s">
+        <v>32</v>
+      </c>
+      <c r="N23" s="8">
+        <v>3597674</v>
+      </c>
+      <c r="O23" s="8">
+        <v>8.8700000000000001E-2</v>
+      </c>
+    </row>
+    <row r="24" spans="12:15">
+      <c r="L24">
+        <v>805</v>
+      </c>
+      <c r="M24" t="s">
+        <v>33</v>
+      </c>
+      <c r="N24" s="8">
+        <v>3127844</v>
+      </c>
+      <c r="O24" s="8">
+        <v>5.8500000000000003E-2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>